--- a/testdata/Financials2.xlsx
+++ b/testdata/Financials2.xlsx
@@ -181,7 +181,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5643" uniqueCount="429">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5685" uniqueCount="429">
   <si>
     <t>ITEM_NAME</t>
   </si>

--- a/testdata/Financials2.xlsx
+++ b/testdata/Financials2.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2520" windowWidth="15150" windowHeight="6540" firstSheet="124" activeTab="125"/>
+    <workbookView xWindow="0" yWindow="2520" windowWidth="15150" windowHeight="6540" firstSheet="151" activeTab="151"/>
   </bookViews>
   <sheets>
     <sheet name="PR Details" sheetId="1" r:id="rId1"/>
@@ -5718,10 +5718,10 @@
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" t="s">
-        <v>370</v>
+        <v>310</v>
       </c>
       <c r="H2" t="s">
-        <v>370</v>
+        <v>310</v>
       </c>
       <c r="I2" s="59">
         <f>ROUND(SUM(G2+H2),2)</f>
@@ -5747,10 +5747,10 @@
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" t="s">
-        <v>370</v>
+        <v>310</v>
       </c>
       <c r="H3" t="s">
-        <v>370</v>
+        <v>310</v>
       </c>
       <c r="I3" s="59">
         <f>ROUND(SUM(G3+H3),2)</f>
@@ -24124,10 +24124,10 @@
         <v>303</v>
       </c>
       <c r="AA2" t="s">
-        <v>370</v>
+        <v>310</v>
       </c>
       <c r="AB2" t="s">
-        <v>370</v>
+        <v>310</v>
       </c>
       <c r="AC2">
         <f>ROUND(SUM((AA2*L2)+(AB2*L2)+(I2*L2)),2)</f>
@@ -24201,10 +24201,10 @@
         <v>303</v>
       </c>
       <c r="AA3" t="s">
-        <v>370</v>
+        <v>310</v>
       </c>
       <c r="AB3" t="s">
-        <v>370</v>
+        <v>310</v>
       </c>
       <c r="AC3">
         <f>ROUND(SUM((AA3*L3)+(AB3*L3)+(I3*L3)),2)</f>
@@ -24431,7 +24431,7 @@
         <v>303</v>
       </c>
       <c r="AA2" t="s">
-        <v>310</v>
+        <v>370</v>
       </c>
       <c r="AB2" t="s">
         <v>310</v>
@@ -24511,7 +24511,7 @@
         <v>310</v>
       </c>
       <c r="AB3" t="s">
-        <v>310</v>
+        <v>370</v>
       </c>
       <c r="AC3">
         <f>ROUND(SUM((AA3*L3)+(AB3*L3)+(I3*L3)),2)</f>
